--- a/summary/COL/COL_INST_export.xlsx
+++ b/summary/COL/COL_INST_export.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Trust Index" sheetId="4" r:id="rId4"/>
     <sheet name="Sampling_age" sheetId="5" r:id="rId5"/>
     <sheet name="Sampling_Gender" sheetId="6" r:id="rId6"/>
-    <sheet name="Sampling_Geo" sheetId="7" r:id="rId7"/>
+    <sheet name="Sampling_Geo_1" sheetId="7" r:id="rId7"/>
     <sheet name="Sampling_type" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2430,7 +2430,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2513,6 +2513,19 @@
       </c>
       <c r="C6">
         <v>13.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>888</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2601,7 +2614,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D149"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2612,15 +2625,10 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Admin2</t>
+          <t>Total Respondents</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Total Respondents</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
@@ -2629,2665 +2637,404 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Leticia</t>
-        </is>
+          <t>Valle Del Cauca</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>133</v>
       </c>
       <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>100</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>48</v>
       </c>
       <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>100</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Antioquia</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Medellín</t>
-        </is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>46</v>
       </c>
       <c r="C4">
-        <v>22</v>
-      </c>
-      <c r="D4">
-        <v>84.59999999999999</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Antioquia</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Caldas (Antioquia)</t>
-        </is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>46</v>
       </c>
       <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Antioquia</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>La Estrella (Antioquia)</t>
-        </is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>36</v>
       </c>
       <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Antioquia</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Sabaneta</t>
-        </is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>35</v>
       </c>
       <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Antioquia</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Santa Rosa de Osos</t>
-        </is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>35</v>
       </c>
       <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Antioquia</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>31</v>
       </c>
       <c r="C9">
-        <v>26</v>
-      </c>
-      <c r="D9">
-        <v>100</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Arauca</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Tame</t>
-        </is>
+          <t>Norte De Santander</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>29</v>
       </c>
       <c r="C10">
-        <v>17</v>
-      </c>
-      <c r="D10">
-        <v>85</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Arauca</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Arauca</t>
-        </is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>27</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
-      <c r="D11">
-        <v>15</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Arauca</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>26</v>
       </c>
       <c r="C12">
-        <v>20</v>
-      </c>
-      <c r="D12">
-        <v>100</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Atlántico</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Barranquilla</t>
-        </is>
+          <t>Chocó</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>26</v>
       </c>
       <c r="C13">
-        <v>47</v>
-      </c>
-      <c r="D13">
-        <v>97.90000000000001</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Atlántico</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Baranoa</t>
-        </is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>26</v>
       </c>
       <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Atlántico</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>26</v>
       </c>
       <c r="C15">
-        <v>48</v>
-      </c>
-      <c r="D15">
-        <v>100</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bolívar</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Cartagena de Indias</t>
-        </is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>24</v>
       </c>
       <c r="C16">
-        <v>20</v>
-      </c>
-      <c r="D16">
-        <v>100</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bolívar</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>23</v>
       </c>
       <c r="C17">
-        <v>20</v>
-      </c>
-      <c r="D17">
-        <v>100</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Tunja</t>
-        </is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>23</v>
       </c>
       <c r="C18">
-        <v>24</v>
-      </c>
-      <c r="D18">
-        <v>100</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>22</v>
       </c>
       <c r="C19">
-        <v>24</v>
-      </c>
-      <c r="D19">
-        <v>100</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Caldas</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Manizales</t>
-        </is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>21</v>
       </c>
       <c r="C20">
-        <v>25</v>
-      </c>
-      <c r="D20">
-        <v>92.59999999999999</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Caldas</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Aguadas</t>
-        </is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>21</v>
       </c>
       <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Caldas</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Villamaría</t>
-        </is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>20</v>
       </c>
       <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Caldas</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>20</v>
       </c>
       <c r="C23">
-        <v>27</v>
-      </c>
-      <c r="D23">
-        <v>100</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Caquetá</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Florencia (Caquetá)</t>
-        </is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>20</v>
       </c>
       <c r="C24">
-        <v>34</v>
-      </c>
-      <c r="D24">
-        <v>97.09999999999999</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Caquetá</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>San Vicente del Caguán</t>
-        </is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>19</v>
       </c>
       <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Caquetá</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
+          <t>Guaviare</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>19</v>
       </c>
       <c r="C26">
-        <v>35</v>
-      </c>
-      <c r="D26">
-        <v>100</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Casanare</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Yopal</t>
-        </is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>19</v>
       </c>
       <c r="C27">
-        <v>39</v>
-      </c>
-      <c r="D27">
-        <v>84.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Casanare</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Aguazul</t>
-        </is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>19</v>
       </c>
       <c r="C28">
-        <v>2</v>
-      </c>
-      <c r="D28">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Casanare</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Tauramena</t>
-        </is>
+          <t>Guainía</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>15</v>
       </c>
       <c r="C29">
-        <v>2</v>
-      </c>
-      <c r="D29">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Casanare</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Maní</t>
-        </is>
+          <t>San Andrés y Providencia</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>15</v>
       </c>
       <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Casanare</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Paz de Ariporo</t>
-        </is>
+          <t>Vichada</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>14</v>
       </c>
       <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="D31">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Casanare</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>San Luis de Palenque</t>
-        </is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>4</v>
       </c>
       <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Casanare</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C33">
-        <v>46</v>
-      </c>
-      <c r="D33">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Cauca</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Popayán</t>
-        </is>
-      </c>
-      <c r="C34">
-        <v>12</v>
-      </c>
-      <c r="D34">
-        <v>57.1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Cauca</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Puracé</t>
-        </is>
-      </c>
-      <c r="C35">
-        <v>3</v>
-      </c>
-      <c r="D35">
-        <v>14.3</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Cauca</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Silvia</t>
-        </is>
-      </c>
-      <c r="C36">
-        <v>3</v>
-      </c>
-      <c r="D36">
-        <v>14.3</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Cauca</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Inzá</t>
-        </is>
-      </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Cauca</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Jambaló</t>
-        </is>
-      </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Cauca</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Totoró</t>
-        </is>
-      </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Cauca</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C40">
-        <v>21</v>
-      </c>
-      <c r="D40">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Cesar</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Valledupar</t>
-        </is>
-      </c>
-      <c r="C41">
-        <v>9</v>
-      </c>
-      <c r="D41">
-        <v>47.4</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Cesar</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Becerril</t>
-        </is>
-      </c>
-      <c r="C42">
-        <v>2</v>
-      </c>
-      <c r="D42">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Cesar</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>La Paz (Cesar)</t>
-        </is>
-      </c>
-      <c r="C43">
-        <v>2</v>
-      </c>
-      <c r="D43">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Cesar</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Pueblo Bello</t>
-        </is>
-      </c>
-      <c r="C44">
-        <v>2</v>
-      </c>
-      <c r="D44">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Cesar</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Bosconia</t>
-        </is>
-      </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-      <c r="D45">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Cesar</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Curumaní</t>
-        </is>
-      </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-      <c r="D46">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Cesar</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Manaure Balcón del Cesar</t>
-        </is>
-      </c>
-      <c r="C47">
-        <v>1</v>
-      </c>
-      <c r="D47">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Cesar</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Tamalameque</t>
-        </is>
-      </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-      <c r="D48">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Cesar</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C49">
-        <v>19</v>
-      </c>
-      <c r="D49">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Chocó</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Istmina</t>
-        </is>
-      </c>
-      <c r="C50">
-        <v>10</v>
-      </c>
-      <c r="D50">
-        <v>38.5</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Chocó</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Condoto</t>
-        </is>
-      </c>
-      <c r="C51">
-        <v>9</v>
-      </c>
-      <c r="D51">
-        <v>34.6</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Chocó</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Quibdó</t>
-        </is>
-      </c>
-      <c r="C52">
-        <v>7</v>
-      </c>
-      <c r="D52">
-        <v>26.9</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Chocó</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C53">
-        <v>26</v>
-      </c>
-      <c r="D53">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Cundinamarca</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Caimito</t>
-        </is>
-      </c>
-      <c r="C54">
-        <v>16</v>
-      </c>
-      <c r="D54">
-        <v>51.6</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Cundinamarca</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Chía</t>
-        </is>
-      </c>
-      <c r="C55">
-        <v>8</v>
-      </c>
-      <c r="D55">
-        <v>25.8</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Cundinamarca</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Chocontá</t>
-        </is>
-      </c>
-      <c r="C56">
-        <v>2</v>
-      </c>
-      <c r="D56">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Cundinamarca</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Vergara</t>
-        </is>
-      </c>
-      <c r="C57">
-        <v>2</v>
-      </c>
-      <c r="D57">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Cundinamarca</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Villeta</t>
-        </is>
-      </c>
-      <c r="C58">
-        <v>2</v>
-      </c>
-      <c r="D58">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Cundinamarca</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Zipaquirá</t>
-        </is>
-      </c>
-      <c r="C59">
-        <v>1</v>
-      </c>
-      <c r="D59">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Cundinamarca</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C60">
-        <v>31</v>
-      </c>
-      <c r="D60">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Córdoba</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Montería</t>
-        </is>
-      </c>
-      <c r="C61">
-        <v>23</v>
-      </c>
-      <c r="D61">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Córdoba</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C62">
-        <v>23</v>
-      </c>
-      <c r="D62">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Guainía</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Inírida</t>
-        </is>
-      </c>
-      <c r="C63">
-        <v>15</v>
-      </c>
-      <c r="D63">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Guainía</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C64">
-        <v>15</v>
-      </c>
-      <c r="D64">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Guaviare</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>San José del Guaviare</t>
-        </is>
-      </c>
-      <c r="C65">
-        <v>15</v>
-      </c>
-      <c r="D65">
-        <v>78.90000000000001</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Guaviare</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>El Retorno</t>
-        </is>
-      </c>
-      <c r="C66">
-        <v>2</v>
-      </c>
-      <c r="D66">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Guaviare</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Calamar (Guaviare)</t>
-        </is>
-      </c>
-      <c r="C67">
-        <v>1</v>
-      </c>
-      <c r="D67">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Guaviare</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Miraflores (Guaviare)</t>
-        </is>
-      </c>
-      <c r="C68">
-        <v>1</v>
-      </c>
-      <c r="D68">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Guaviare</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C69">
-        <v>19</v>
-      </c>
-      <c r="D69">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Huila</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Neiva</t>
-        </is>
-      </c>
-      <c r="C70">
-        <v>11</v>
-      </c>
-      <c r="D70">
-        <v>57.9</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Huila</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Garzón</t>
-        </is>
-      </c>
-      <c r="C71">
-        <v>5</v>
-      </c>
-      <c r="D71">
-        <v>26.3</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Huila</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>La Plata (Huila)</t>
-        </is>
-      </c>
-      <c r="C72">
-        <v>3</v>
-      </c>
-      <c r="D72">
-        <v>15.8</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Huila</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C73">
-        <v>19</v>
-      </c>
-      <c r="D73">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>La Guajira</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Riohacha</t>
-        </is>
-      </c>
-      <c r="C74">
-        <v>23</v>
-      </c>
-      <c r="D74">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>La Guajira</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C75">
-        <v>23</v>
-      </c>
-      <c r="D75">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Magdalena</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Santa Marta</t>
-        </is>
-      </c>
-      <c r="C76">
-        <v>15</v>
-      </c>
-      <c r="D76">
-        <v>57.7</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Magdalena</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Ciénaga</t>
-        </is>
-      </c>
-      <c r="C77">
-        <v>6</v>
-      </c>
-      <c r="D77">
-        <v>23.1</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Magdalena</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>El Piñón</t>
-        </is>
-      </c>
-      <c r="C78">
-        <v>1</v>
-      </c>
-      <c r="D78">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Magdalena</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Guamal (Magdalena)</t>
-        </is>
-      </c>
-      <c r="C79">
-        <v>1</v>
-      </c>
-      <c r="D79">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Magdalena</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Plato</t>
-        </is>
-      </c>
-      <c r="C80">
-        <v>1</v>
-      </c>
-      <c r="D80">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Magdalena</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Puebloviejo (Magdalena)</t>
-        </is>
-      </c>
-      <c r="C81">
-        <v>1</v>
-      </c>
-      <c r="D81">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Magdalena</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Zona Bananera</t>
-        </is>
-      </c>
-      <c r="C82">
-        <v>1</v>
-      </c>
-      <c r="D82">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Magdalena</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C83">
-        <v>26</v>
-      </c>
-      <c r="D83">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Villavicencio</t>
-        </is>
-      </c>
-      <c r="C84">
-        <v>31</v>
-      </c>
-      <c r="D84">
-        <v>67.40000000000001</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Restrepo (Meta)</t>
-        </is>
-      </c>
-      <c r="C85">
-        <v>6</v>
-      </c>
-      <c r="D85">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Cabuyaro</t>
-        </is>
-      </c>
-      <c r="C86">
-        <v>4</v>
-      </c>
-      <c r="D86">
-        <v>8.699999999999999</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Puerto Gaitán</t>
-        </is>
-      </c>
-      <c r="C87">
-        <v>2</v>
-      </c>
-      <c r="D87">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>San Martín (Meta)</t>
-        </is>
-      </c>
-      <c r="C88">
-        <v>2</v>
-      </c>
-      <c r="D88">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Acacías</t>
-        </is>
-      </c>
-      <c r="C89">
-        <v>1</v>
-      </c>
-      <c r="D89">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C90">
-        <v>46</v>
-      </c>
-      <c r="D90">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Nariño</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Pasto</t>
-        </is>
-      </c>
-      <c r="C91">
-        <v>15</v>
-      </c>
-      <c r="D91">
-        <v>78.90000000000001</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Nariño</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Cumbal</t>
-        </is>
-      </c>
-      <c r="C92">
-        <v>4</v>
-      </c>
-      <c r="D92">
-        <v>21.1</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Nariño</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C93">
-        <v>19</v>
-      </c>
-      <c r="D93">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Norte De Santander</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>San José de Cúcuta</t>
-        </is>
-      </c>
-      <c r="C94">
-        <v>16</v>
-      </c>
-      <c r="D94">
-        <v>55.2</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Norte De Santander</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Villa del Rosario</t>
-        </is>
-      </c>
-      <c r="C95">
-        <v>10</v>
-      </c>
-      <c r="D95">
-        <v>34.5</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Norte De Santander</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Pamplona</t>
-        </is>
-      </c>
-      <c r="C96">
-        <v>3</v>
-      </c>
-      <c r="D96">
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Norte De Santander</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C97">
-        <v>29</v>
-      </c>
-      <c r="D97">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Putumayo</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Sibundoy</t>
-        </is>
-      </c>
-      <c r="C98">
-        <v>14</v>
-      </c>
-      <c r="D98">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Putumayo</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Puerto Asís</t>
-        </is>
-      </c>
-      <c r="C99">
-        <v>6</v>
-      </c>
-      <c r="D99">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Putumayo</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C100">
-        <v>20</v>
-      </c>
-      <c r="D100">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Quindío</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Armenia (Quindío)</t>
-        </is>
-      </c>
-      <c r="C101">
-        <v>18</v>
-      </c>
-      <c r="D101">
-        <v>81.8</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Quindío</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Salento</t>
-        </is>
-      </c>
-      <c r="C102">
-        <v>2</v>
-      </c>
-      <c r="D102">
-        <v>9.1</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Quindío</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Circasia</t>
-        </is>
-      </c>
-      <c r="C103">
-        <v>1</v>
-      </c>
-      <c r="D103">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Quindío</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Filandia</t>
-        </is>
-      </c>
-      <c r="C104">
-        <v>1</v>
-      </c>
-      <c r="D104">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Quindío</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C105">
-        <v>22</v>
-      </c>
-      <c r="D105">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Risaralda</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Belén de Umbría</t>
-        </is>
-      </c>
-      <c r="C106">
-        <v>7</v>
-      </c>
-      <c r="D106">
-        <v>33.3</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Risaralda</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Pereira</t>
-        </is>
-      </c>
-      <c r="C107">
-        <v>6</v>
-      </c>
-      <c r="D107">
-        <v>28.6</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Risaralda</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Mistrató</t>
-        </is>
-      </c>
-      <c r="C108">
-        <v>3</v>
-      </c>
-      <c r="D108">
-        <v>14.3</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Risaralda</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>La Virginia</t>
-        </is>
-      </c>
-      <c r="C109">
-        <v>2</v>
-      </c>
-      <c r="D109">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Risaralda</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>La Celia</t>
-        </is>
-      </c>
-      <c r="C110">
-        <v>1</v>
-      </c>
-      <c r="D110">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Risaralda</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Marsella</t>
-        </is>
-      </c>
-      <c r="C111">
-        <v>1</v>
-      </c>
-      <c r="D111">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Risaralda</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Santa Rosa de Cabal</t>
-        </is>
-      </c>
-      <c r="C112">
-        <v>1</v>
-      </c>
-      <c r="D112">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Risaralda</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C113">
-        <v>21</v>
-      </c>
-      <c r="D113">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>San Andrés y Providencia</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>San Andrés (San Andrés y Providencia)</t>
-        </is>
-      </c>
-      <c r="C114">
-        <v>15</v>
-      </c>
-      <c r="D114">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>San Andrés y Providencia</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C115">
-        <v>15</v>
-      </c>
-      <c r="D115">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Santander</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Bucaramanga</t>
-        </is>
-      </c>
-      <c r="C116">
-        <v>23</v>
-      </c>
-      <c r="D116">
-        <v>63.9</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Santander</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Barrancabermeja</t>
-        </is>
-      </c>
-      <c r="C117">
-        <v>8</v>
-      </c>
-      <c r="D117">
-        <v>22.2</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Santander</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Floridablanca</t>
-        </is>
-      </c>
-      <c r="C118">
-        <v>4</v>
-      </c>
-      <c r="D118">
-        <v>11.1</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Santander</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Málaga</t>
-        </is>
-      </c>
-      <c r="C119">
-        <v>1</v>
-      </c>
-      <c r="D119">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Santander</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C120">
-        <v>36</v>
-      </c>
-      <c r="D120">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Sucre</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Sincelejo</t>
-        </is>
-      </c>
-      <c r="C121">
-        <v>26</v>
-      </c>
-      <c r="D121">
-        <v>74.3</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Sucre</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>San Luis de Sincé</t>
-        </is>
-      </c>
-      <c r="C122">
-        <v>7</v>
-      </c>
-      <c r="D122">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Sucre</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Corozal</t>
-        </is>
-      </c>
-      <c r="C123">
-        <v>1</v>
-      </c>
-      <c r="D123">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Sucre</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>San José de Toluviejo</t>
-        </is>
-      </c>
-      <c r="C124">
-        <v>1</v>
-      </c>
-      <c r="D124">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Sucre</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C125">
-        <v>35</v>
-      </c>
-      <c r="D125">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Tolima</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Ibagué</t>
-        </is>
-      </c>
-      <c r="C126">
-        <v>24</v>
-      </c>
-      <c r="D126">
-        <v>92.3</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Tolima</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Líbano</t>
-        </is>
-      </c>
-      <c r="C127">
-        <v>1</v>
-      </c>
-      <c r="D127">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Tolima</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Melgar (Tolima)</t>
-        </is>
-      </c>
-      <c r="C128">
-        <v>1</v>
-      </c>
-      <c r="D128">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Tolima</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C129">
-        <v>26</v>
-      </c>
-      <c r="D129">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Valle Del Cauca</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Andalucía</t>
-        </is>
-      </c>
-      <c r="C130">
-        <v>38</v>
-      </c>
-      <c r="D130">
-        <v>28.6</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Valle Del Cauca</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Cali</t>
-        </is>
-      </c>
-      <c r="C131">
-        <v>38</v>
-      </c>
-      <c r="D131">
-        <v>28.6</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Valle Del Cauca</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Florida (Valle del Cauca)</t>
-        </is>
-      </c>
-      <c r="C132">
-        <v>12</v>
-      </c>
-      <c r="D132">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Valle Del Cauca</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Palmira</t>
-        </is>
-      </c>
-      <c r="C133">
-        <v>8</v>
-      </c>
-      <c r="D133">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Valle Del Cauca</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Cartago</t>
-        </is>
-      </c>
-      <c r="C134">
-        <v>6</v>
-      </c>
-      <c r="D134">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Valle Del Cauca</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Bugalagrande</t>
-        </is>
-      </c>
-      <c r="C135">
-        <v>4</v>
-      </c>
-      <c r="D135">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Valle Del Cauca</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Jamundí</t>
-        </is>
-      </c>
-      <c r="C136">
-        <v>4</v>
-      </c>
-      <c r="D136">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Valle Del Cauca</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Tuluá</t>
-        </is>
-      </c>
-      <c r="C137">
-        <v>4</v>
-      </c>
-      <c r="D137">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Valle Del Cauca</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Obando</t>
-        </is>
-      </c>
-      <c r="C138">
-        <v>3</v>
-      </c>
-      <c r="D138">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Valle Del Cauca</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Toro</t>
-        </is>
-      </c>
-      <c r="C139">
-        <v>3</v>
-      </c>
-      <c r="D139">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Valle Del Cauca</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Yumbo</t>
-        </is>
-      </c>
-      <c r="C140">
-        <v>3</v>
-      </c>
-      <c r="D140">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Valle Del Cauca</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Zarzal</t>
-        </is>
-      </c>
-      <c r="C141">
-        <v>3</v>
-      </c>
-      <c r="D141">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Valle Del Cauca</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Buenaventura</t>
-        </is>
-      </c>
-      <c r="C142">
-        <v>2</v>
-      </c>
-      <c r="D142">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Valle Del Cauca</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Roldanillo</t>
-        </is>
-      </c>
-      <c r="C143">
-        <v>2</v>
-      </c>
-      <c r="D143">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Valle Del Cauca</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Alcalá (Valle del Cauca)</t>
-        </is>
-      </c>
-      <c r="C144">
-        <v>1</v>
-      </c>
-      <c r="D144">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Valle Del Cauca</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Guacarí</t>
-        </is>
-      </c>
-      <c r="C145">
-        <v>1</v>
-      </c>
-      <c r="D145">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Valle Del Cauca</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Riofrío</t>
-        </is>
-      </c>
-      <c r="C146">
-        <v>1</v>
-      </c>
-      <c r="D146">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Valle Del Cauca</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C147">
-        <v>133</v>
-      </c>
-      <c r="D147">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Vichada</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Puerto Carreño</t>
-        </is>
-      </c>
-      <c r="C148">
-        <v>14</v>
-      </c>
-      <c r="D148">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Vichada</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C149">
-        <v>14</v>
-      </c>
-      <c r="D149">
-        <v>100</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
